--- a/TurboVault_TPCH_Data.xlsx
+++ b/TurboVault_TPCH_Data.xlsx
@@ -979,7 +979,7 @@
         <v>SRC0004</v>
       </c>
       <c r="D3" t="str">
-        <v>C_CustomerKey</v>
+        <v>L_SUPPKEY</v>
       </c>
       <c r="E3" t="str">
         <v>C_CUSTKEY</v>
@@ -2786,7 +2786,7 @@
         <v>CUSTOMER_H</v>
       </c>
       <c r="G2" t="str">
-        <v>address_type</v>
+        <v>C_MKTSEGMENT</v>
       </c>
       <c r="H2" t="str">
         <v>customer_name</v>
@@ -2821,7 +2821,7 @@
         <v>CUSTOMER_H</v>
       </c>
       <c r="G3" t="str">
-        <v>address_type</v>
+        <v>C_MKTSEGMENT</v>
       </c>
       <c r="H3" t="str">
         <v>c_nationkey</v>
@@ -2853,7 +2853,7 @@
         <v>CUSTOMER_H</v>
       </c>
       <c r="G4" t="str">
-        <v>address_type</v>
+        <v>C_MKTSEGMENT</v>
       </c>
       <c r="I4" t="str">
         <v>3</v>
@@ -3521,7 +3521,7 @@
         <v>SRC0004</v>
       </c>
       <c r="D3" t="str">
-        <v>l_shipisntruct</v>
+        <v>l_shipinstruct</v>
       </c>
       <c r="E3" t="str">
         <v>NH0001</v>

--- a/TurboVault_TPCH_Data.xlsx
+++ b/TurboVault_TPCH_Data.xlsx
@@ -3613,7 +3613,7 @@
         <v>RS001</v>
       </c>
       <c r="E2" t="str">
-        <v>n_nationkey,r_regionkey</v>
+        <v>n_comment,n_regionkey</v>
       </c>
       <c r="G2" t="str">
         <v>latest</v>
@@ -3636,7 +3636,7 @@
         <v>RS002</v>
       </c>
       <c r="F3" t="str">
-        <v>n_nationkey,r_regionkey</v>
+        <v>n_comment,n_regionkey</v>
       </c>
       <c r="G3" t="str">
         <v>latest</v>

--- a/TurboVault_TPCH_Data.xlsx
+++ b/TurboVault_TPCH_Data.xlsx
@@ -979,7 +979,7 @@
         <v>SRC0004</v>
       </c>
       <c r="D3" t="str">
-        <v>C_CustomerKey</v>
+        <v>L_SUPPKEY</v>
       </c>
       <c r="E3" t="str">
         <v>C_CUSTKEY</v>
@@ -2786,7 +2786,7 @@
         <v>CUSTOMER_H</v>
       </c>
       <c r="G2" t="str">
-        <v>address_type</v>
+        <v>C_MKTSEGMENT</v>
       </c>
       <c r="H2" t="str">
         <v>customer_name</v>
@@ -2821,7 +2821,7 @@
         <v>CUSTOMER_H</v>
       </c>
       <c r="G3" t="str">
-        <v>address_type</v>
+        <v>C_MKTSEGMENT</v>
       </c>
       <c r="H3" t="str">
         <v>c_nationkey</v>
@@ -2853,7 +2853,7 @@
         <v>CUSTOMER_H</v>
       </c>
       <c r="G4" t="str">
-        <v>address_type</v>
+        <v>C_MKTSEGMENT</v>
       </c>
       <c r="I4" t="str">
         <v>3</v>
@@ -3521,7 +3521,7 @@
         <v>SRC0004</v>
       </c>
       <c r="D3" t="str">
-        <v>l_shipisntruct</v>
+        <v>l_shipinstruct</v>
       </c>
       <c r="E3" t="str">
         <v>NH0001</v>
@@ -3613,7 +3613,7 @@
         <v>RS001</v>
       </c>
       <c r="E2" t="str">
-        <v>n_nationkey,r_regionkey</v>
+        <v>n_comment,n_regionkey</v>
       </c>
       <c r="G2" t="str">
         <v>latest</v>
@@ -3636,7 +3636,7 @@
         <v>RS002</v>
       </c>
       <c r="F3" t="str">
-        <v>n_nationkey,r_regionkey</v>
+        <v>n_comment,n_regionkey</v>
       </c>
       <c r="G3" t="str">
         <v>latest</v>

--- a/TurboVault_TPCH_Data.xlsx
+++ b/TurboVault_TPCH_Data.xlsx
@@ -1968,7 +1968,7 @@
         <v>C_ACCTBAL</v>
       </c>
       <c r="H2" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="str">
         <v>Customers</v>
@@ -2026,7 +2026,7 @@
         <v>C_COMMENT</v>
       </c>
       <c r="H4" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
         <v>Customers</v>

--- a/TurboVault_TPCH_Data.xlsx
+++ b/TurboVault_TPCH_Data.xlsx
@@ -1,36 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\obause\Documents\repos\turbovault-integration\turbovault-engine\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBC1EB3-2A79-4CB0-9870-33D5C97D0DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3612" yWindow="2244" windowWidth="20160" windowHeight="11760" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="source_data" sheetId="1" r:id="rId1"/>
-    <sheet name="standard_hub" sheetId="2" r:id="rId2"/>
-    <sheet name="standard_link" sheetId="3" r:id="rId3"/>
-    <sheet name="standard_satellite" sheetId="4" r:id="rId4"/>
-    <sheet name="multiactive_satellite" sheetId="5" r:id="rId5"/>
-    <sheet name="non_historized_link" sheetId="6" r:id="rId6"/>
-    <sheet name="non_historized_satellite" sheetId="7" r:id="rId7"/>
-    <sheet name="ref_table" sheetId="8" r:id="rId8"/>
-    <sheet name="ref_hub" sheetId="9" r:id="rId9"/>
-    <sheet name="ref_sat" sheetId="10" r:id="rId10"/>
-    <sheet name="pit" sheetId="11" r:id="rId11"/>
+    <sheet r:id="rId1" sheetId="1" name="source_data"/>
+    <sheet r:id="rId2" sheetId="2" name="standard_hub"/>
+    <sheet r:id="rId3" sheetId="3" name="standard_link"/>
+    <sheet r:id="rId4" sheetId="4" name="standard_satellite"/>
+    <sheet r:id="rId5" sheetId="5" name="multiactive_satellite"/>
+    <sheet r:id="rId6" sheetId="6" name="non_historized_link"/>
+    <sheet r:id="rId7" sheetId="7" name="non_historized_satellite"/>
+    <sheet r:id="rId8" sheetId="8" name="ref_table"/>
+    <sheet r:id="rId9" sheetId="9" name="ref_hub"/>
+    <sheet r:id="rId10" sheetId="10" name="ref_sat"/>
+    <sheet r:id="rId11" sheetId="11" name="pit"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="282">
   <si>
     <t>Pit_Identifier</t>
   </si>
@@ -773,9 +767,6 @@
     <t>Is_Primary_Source</t>
   </si>
   <si>
-    <t>Target_Role_Primary_Key_Physical_Name</t>
-  </si>
-  <si>
     <t>C_CUSTKEY</t>
   </si>
   <si>
@@ -827,9 +818,6 @@
     <t>Source_System</t>
   </si>
   <si>
-    <t>Source_Object</t>
-  </si>
-  <si>
     <t>Source_Schema_Physical_Name</t>
   </si>
   <si>
@@ -855,9 +843,6 @@
   </si>
   <si>
     <t>sysdate()</t>
-  </si>
-  <si>
-    <t>sources</t>
   </si>
   <si>
     <t>!Orders</t>
@@ -890,7 +875,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -920,20 +906,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -944,10 +933,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -985,71 +974,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1077,7 +1066,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1100,11 +1089,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1113,13 +1102,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1129,7 +1118,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1138,7 +1127,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1147,7 +1136,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1155,10 +1144,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1223,275 +1212,227 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="H1" t="s">
+      <c r="C2" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F2" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="F3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="I2" t="s">
+      <c r="F4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="F5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F3" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H3" t="s">
-        <v>274</v>
-      </c>
-      <c r="I3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" t="s">
-        <v>271</v>
-      </c>
-      <c r="C4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E6" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F4" t="s">
-        <v>277</v>
-      </c>
-      <c r="G4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H4" t="s">
-        <v>274</v>
-      </c>
-      <c r="I4" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F5" t="s">
-        <v>278</v>
-      </c>
-      <c r="G5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H5" t="s">
-        <v>274</v>
-      </c>
-      <c r="I5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C6" t="s">
-        <v>279</v>
-      </c>
-      <c r="D6" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E6" t="s">
-        <v>279</v>
-      </c>
-      <c r="F6" t="s">
-        <v>280</v>
-      </c>
-      <c r="G6" t="s">
-        <v>279</v>
-      </c>
-      <c r="H6" t="s">
-        <v>274</v>
-      </c>
-      <c r="I6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" t="s">
-        <v>271</v>
-      </c>
-      <c r="C7" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F9" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="E7" t="s">
-        <v>281</v>
-      </c>
-      <c r="F7" t="s">
-        <v>282</v>
-      </c>
-      <c r="G7" t="s">
-        <v>281</v>
-      </c>
-      <c r="H7" t="s">
-        <v>274</v>
-      </c>
-      <c r="I7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E8" t="s">
-        <v>256</v>
-      </c>
-      <c r="F8" t="s">
-        <v>283</v>
-      </c>
-      <c r="G8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H8" t="s">
-        <v>274</v>
-      </c>
-      <c r="I8" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>271</v>
-      </c>
-      <c r="C9" t="s">
-        <v>227</v>
-      </c>
-      <c r="D9" t="s">
-        <v>272</v>
-      </c>
-      <c r="E9" t="s">
-        <v>227</v>
-      </c>
-      <c r="F9" t="s">
-        <v>284</v>
-      </c>
-      <c r="G9" t="s">
-        <v>227</v>
-      </c>
-      <c r="H9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I9" t="s">
-        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -1500,153 +1441,158 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1656,65 +1602,72 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1724,493 +1677,505 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="L1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F2" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J4" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="K4" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" t="s">
-        <v>248</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
-        <v>153</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="J5" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" t="s">
+      <c r="G6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" t="s">
-        <v>209</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="I6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="J6" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E5" t="s">
-        <v>251</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="J7" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="J8" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E6" t="s">
-        <v>253</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="J9" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="J10" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B7" t="s">
-        <v>254</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="G13" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K13" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D14" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E14" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" t="s">
-        <v>236</v>
-      </c>
-      <c r="H7" t="s">
-        <v>87</v>
-      </c>
-      <c r="I7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" t="s">
-        <v>256</v>
-      </c>
-      <c r="L7" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>235</v>
-      </c>
-      <c r="B8" t="s">
-        <v>254</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>220</v>
-      </c>
-      <c r="E8" t="s">
-        <v>258</v>
-      </c>
-      <c r="F8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" t="s">
-        <v>236</v>
-      </c>
-      <c r="H8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I8" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" t="s">
-        <v>256</v>
-      </c>
-      <c r="L8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>259</v>
-      </c>
-      <c r="B9" t="s">
-        <v>260</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>229</v>
-      </c>
-      <c r="E9" t="s">
-        <v>255</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" t="s">
-        <v>236</v>
-      </c>
-      <c r="H9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" t="s">
-        <v>256</v>
-      </c>
-      <c r="L9" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>259</v>
-      </c>
-      <c r="B10" t="s">
-        <v>260</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>220</v>
-      </c>
-      <c r="E10" t="s">
-        <v>258</v>
-      </c>
-      <c r="F10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" t="s">
-        <v>236</v>
-      </c>
-      <c r="H10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" t="s">
-        <v>256</v>
-      </c>
-      <c r="L10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B11" t="s">
-        <v>260</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>221</v>
-      </c>
-      <c r="E11" t="s">
-        <v>255</v>
-      </c>
-      <c r="F11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" t="s">
-        <v>236</v>
-      </c>
-      <c r="H11" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" t="s">
-        <v>87</v>
-      </c>
-      <c r="J11" t="s">
-        <v>256</v>
-      </c>
-      <c r="L11" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>259</v>
-      </c>
-      <c r="B12" t="s">
-        <v>260</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>221</v>
-      </c>
-      <c r="E12" t="s">
-        <v>258</v>
-      </c>
-      <c r="F12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" t="s">
-        <v>236</v>
-      </c>
-      <c r="H12" t="s">
-        <v>87</v>
-      </c>
-      <c r="I12" t="s">
-        <v>87</v>
-      </c>
-      <c r="J12" t="s">
-        <v>256</v>
-      </c>
-      <c r="L12" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>224</v>
-      </c>
-      <c r="B13" t="s">
-        <v>262</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>222</v>
-      </c>
-      <c r="E13" t="s">
-        <v>223</v>
-      </c>
-      <c r="F13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" t="s">
-        <v>225</v>
-      </c>
-      <c r="H13" t="s">
-        <v>87</v>
-      </c>
-      <c r="I13" t="s">
-        <v>27</v>
-      </c>
-      <c r="J13" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>230</v>
-      </c>
-      <c r="B14" t="s">
-        <v>263</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>229</v>
-      </c>
-      <c r="E14" t="s">
-        <v>229</v>
-      </c>
-      <c r="F14" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" t="s">
-        <v>231</v>
-      </c>
-      <c r="H14" t="s">
-        <v>87</v>
-      </c>
-      <c r="I14" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" t="s">
-        <v>256</v>
-      </c>
+      <c r="K14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2218,531 +2183,590 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:P13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I2" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="I3" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K4" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="P4" t="s">
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="I5" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="I6" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P6" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="I8" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O9" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="I10" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O10" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P10" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I11" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O11" t="s">
+      <c r="O11" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P11" t="s">
+      <c r="P11" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="I12" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O12" t="s">
+      <c r="O12" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I13" t="s">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="N13" t="s">
+      <c r="N13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O13" t="s">
+      <c r="O13" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13" s="1" t="s">
         <v>241</v>
       </c>
     </row>
@@ -2752,822 +2776,850 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="J2" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="J3" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="J4" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="J5" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="J6" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="J7" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="J15" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="J16" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="J17" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="J18" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="J19" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="J20" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="J21" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="J22" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="J23" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="J24" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="J25" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="J26" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="1" t="s">
         <v>194</v>
       </c>
+      <c r="J27" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3575,214 +3627,227 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="K3" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I4" t="s">
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I6" t="s">
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="1" t="s">
         <v>137</v>
       </c>
     </row>
@@ -3792,627 +3857,766 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:O18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="15" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I2" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I3" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I4" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K5" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K6" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="N6" t="s">
+      <c r="M6" s="1"/>
+      <c r="N6" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K7" t="s">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="N7" t="s">
+      <c r="M7" s="1"/>
+      <c r="N7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="K8" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="N8" t="s">
+      <c r="M8" s="1"/>
+      <c r="N8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="K9" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N9" t="s">
+      <c r="M9" s="1"/>
+      <c r="N9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O9" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="K10" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="N10" t="s">
+      <c r="M10" s="1"/>
+      <c r="N10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O10" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K11" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="N11" t="s">
+      <c r="M11" s="1"/>
+      <c r="N11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O11" t="s">
+      <c r="O11" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K12" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="N12" t="s">
+      <c r="M12" s="1"/>
+      <c r="N12" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O12" t="s">
+      <c r="O12" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="K13" t="s">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="N13" t="s">
+      <c r="M13" s="1"/>
+      <c r="N13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O13" t="s">
+      <c r="O13" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K14" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="N14" t="s">
+      <c r="M14" s="1"/>
+      <c r="N14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O14" t="s">
+      <c r="O14" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="K15" t="s">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="N15" t="s">
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O15" t="s">
+      <c r="O15" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K16" t="s">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="N16" t="s">
+      <c r="M16" s="1"/>
+      <c r="N16" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O16" t="s">
+      <c r="O16" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="K17" t="s">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N17" t="s">
+      <c r="M17" s="1"/>
+      <c r="N17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O17" t="s">
+      <c r="O17" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4422,85 +4626,94 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4510,93 +4723,98 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>43</v>
       </c>
     </row>

--- a/TurboVault_TPCH_Data.xlsx
+++ b/TurboVault_TPCH_Data.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="283">
   <si>
     <t>Pit_Identifier</t>
   </si>
@@ -762,6 +762,9 @@
   </si>
   <si>
     <t>Business_Key_Physical_Name</t>
+  </si>
+  <si>
+    <t>Effectivity_Satellite</t>
   </si>
   <si>
     <t>Is_Primary_Source</t>
@@ -877,13 +880,25 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -894,7 +909,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -906,13 +928,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1233,22 +1267,22 @@
         <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
@@ -1256,22 +1290,22 @@
         <v>128</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>133</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>133</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -1279,22 +1313,22 @@
         <v>162</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>165</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>165</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -1302,22 +1336,22 @@
         <v>140</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>144</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>144</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -1325,22 +1359,22 @@
         <v>63</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -1348,22 +1382,22 @@
         <v>181</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -1371,22 +1405,22 @@
         <v>190</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -1394,22 +1428,22 @@
         <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -1417,22 +1451,22 @@
         <v>41</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>227</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>227</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -1681,7 +1715,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -1691,10 +1725,11 @@
     <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="16.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="25.290714285714284" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1719,20 +1754,23 @@
       <c r="G1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>130</v>
       </c>
@@ -1743,10 +1781,10 @@
         <v>128</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>27</v>
@@ -1754,17 +1792,20 @@
       <c r="G2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>27</v>
+      <c r="H2" s="4">
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>248</v>
+      <c r="L2" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -1781,7 +1822,7 @@
         <v>92</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>27</v>
@@ -1789,17 +1830,20 @@
       <c r="G3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>248</v>
+      <c r="L3" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -1807,7 +1851,7 @@
         <v>90</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>162</v>
@@ -1824,16 +1868,19 @@
       <c r="G4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
@@ -1846,10 +1893,10 @@
         <v>140</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>27</v>
@@ -1857,32 +1904,35 @@
       <c r="G5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>181</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>27</v>
@@ -1890,23 +1940,26 @@
       <c r="G6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
         <v>235</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>24</v>
@@ -1915,7 +1968,7 @@
         <v>229</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>27</v>
@@ -1923,17 +1976,20 @@
       <c r="G7" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>256</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -1941,7 +1997,7 @@
         <v>235</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>24</v>
@@ -1950,7 +2006,7 @@
         <v>220</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>29</v>
@@ -1958,25 +2014,28 @@
       <c r="G8" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>256</v>
       </c>
+      <c r="L8" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>24</v>
@@ -1985,7 +2044,7 @@
         <v>229</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>27</v>
@@ -1993,25 +2052,28 @@
       <c r="G9" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="K9" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>24</v>
@@ -2020,7 +2082,7 @@
         <v>220</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>29</v>
@@ -2028,25 +2090,28 @@
       <c r="G10" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>41</v>
@@ -2055,7 +2120,7 @@
         <v>221</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>27</v>
@@ -2063,25 +2128,28 @@
       <c r="G11" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>87</v>
+      <c r="H11" s="5">
+        <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>87</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>255</v>
+        <v>87</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>41</v>
@@ -2090,7 +2158,7 @@
         <v>221</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>29</v>
@@ -2098,17 +2166,20 @@
       <c r="G12" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>87</v>
+      <c r="H12" s="5">
+        <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>87</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>255</v>
+        <v>87</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
@@ -2116,7 +2187,7 @@
         <v>224</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>41</v>
@@ -2133,23 +2204,26 @@
       <c r="G13" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1" t="s">
         <v>230</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>24</v>
@@ -2166,16 +2240,19 @@
       <c r="G14" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="K14" s="1"/>
+      <c r="K14" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="L14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2784,12 +2861,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="34.71928571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="29.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>

--- a/TurboVault_TPCH_Data.xlsx
+++ b/TurboVault_TPCH_Data.xlsx
@@ -1,36 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\obause\Documents\repos\turbovault-integration\turbovault-engine\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBC1EB3-2A79-4CB0-9870-33D5C97D0DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3612" yWindow="2244" windowWidth="20160" windowHeight="11760" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="source_data" sheetId="1" r:id="rId1"/>
-    <sheet name="standard_hub" sheetId="2" r:id="rId2"/>
-    <sheet name="standard_link" sheetId="3" r:id="rId3"/>
-    <sheet name="standard_satellite" sheetId="4" r:id="rId4"/>
-    <sheet name="multiactive_satellite" sheetId="5" r:id="rId5"/>
-    <sheet name="non_historized_link" sheetId="6" r:id="rId6"/>
-    <sheet name="non_historized_satellite" sheetId="7" r:id="rId7"/>
-    <sheet name="ref_table" sheetId="8" r:id="rId8"/>
-    <sheet name="ref_hub" sheetId="9" r:id="rId9"/>
-    <sheet name="ref_sat" sheetId="10" r:id="rId10"/>
-    <sheet name="pit" sheetId="11" r:id="rId11"/>
+    <sheet r:id="rId1" sheetId="1" name="source_data"/>
+    <sheet r:id="rId2" sheetId="2" name="standard_hub"/>
+    <sheet r:id="rId3" sheetId="3" name="standard_link"/>
+    <sheet r:id="rId4" sheetId="4" name="standard_satellite"/>
+    <sheet r:id="rId5" sheetId="5" name="multiactive_satellite"/>
+    <sheet r:id="rId6" sheetId="6" name="non_historized_link"/>
+    <sheet r:id="rId7" sheetId="7" name="non_historized_satellite"/>
+    <sheet r:id="rId8" sheetId="8" name="ref_table"/>
+    <sheet r:id="rId9" sheetId="9" name="ref_hub"/>
+    <sheet r:id="rId10" sheetId="10" name="ref_sat"/>
+    <sheet r:id="rId11" sheetId="11" name="pit"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="283">
   <si>
     <t>Pit_Identifier</t>
   </si>
@@ -770,12 +764,12 @@
     <t>Business_Key_Physical_Name</t>
   </si>
   <si>
+    <t>Effectivity_Satellite</t>
+  </si>
+  <si>
     <t>Is_Primary_Source</t>
   </si>
   <si>
-    <t>Target_Role_Primary_Key_Physical_Name</t>
-  </si>
-  <si>
     <t>C_CUSTKEY</t>
   </si>
   <si>
@@ -827,9 +821,6 @@
     <t>Source_System</t>
   </si>
   <si>
-    <t>Source_Object</t>
-  </si>
-  <si>
     <t>Source_Schema_Physical_Name</t>
   </si>
   <si>
@@ -855,9 +846,6 @@
   </si>
   <si>
     <t>sysdate()</t>
-  </si>
-  <si>
-    <t>sources</t>
   </si>
   <si>
     <t>!Orders</t>
@@ -890,14 +878,27 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -908,7 +909,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -920,20 +928,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="7">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -944,10 +967,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -985,71 +1008,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1077,7 +1100,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1100,11 +1123,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1113,13 +1136,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1129,7 +1152,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1138,7 +1161,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1147,7 +1170,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1155,10 +1178,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1223,275 +1246,227 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H2" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="I2" t="s">
+      <c r="F3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="F4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H3" t="s">
-        <v>274</v>
-      </c>
-      <c r="I3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="F5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" t="s">
-        <v>272</v>
-      </c>
-      <c r="E4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="D6" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="G4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H4" t="s">
-        <v>274</v>
-      </c>
-      <c r="I4" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="E6" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" t="s">
-        <v>272</v>
-      </c>
-      <c r="E5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F5" t="s">
-        <v>278</v>
-      </c>
-      <c r="G5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H5" t="s">
-        <v>274</v>
-      </c>
-      <c r="I5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="D7" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C6" t="s">
-        <v>279</v>
-      </c>
-      <c r="D6" t="s">
-        <v>272</v>
-      </c>
-      <c r="E6" t="s">
-        <v>279</v>
-      </c>
-      <c r="F6" t="s">
-        <v>280</v>
-      </c>
-      <c r="G6" t="s">
-        <v>279</v>
-      </c>
-      <c r="H6" t="s">
-        <v>274</v>
-      </c>
-      <c r="I6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="D8" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C7" t="s">
-        <v>281</v>
-      </c>
-      <c r="D7" t="s">
-        <v>272</v>
-      </c>
-      <c r="E7" t="s">
-        <v>281</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="D9" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G7" t="s">
-        <v>281</v>
-      </c>
-      <c r="H7" t="s">
-        <v>274</v>
-      </c>
-      <c r="I7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E8" t="s">
-        <v>256</v>
-      </c>
-      <c r="F8" t="s">
-        <v>283</v>
-      </c>
-      <c r="G8" t="s">
-        <v>256</v>
-      </c>
-      <c r="H8" t="s">
-        <v>274</v>
-      </c>
-      <c r="I8" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>271</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="F9" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D9" t="s">
-        <v>272</v>
-      </c>
-      <c r="E9" t="s">
-        <v>227</v>
-      </c>
-      <c r="F9" t="s">
-        <v>284</v>
-      </c>
-      <c r="G9" t="s">
-        <v>227</v>
-      </c>
-      <c r="H9" t="s">
-        <v>274</v>
-      </c>
-      <c r="I9" t="s">
-        <v>275</v>
+      <c r="G9" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -1500,153 +1475,158 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1656,65 +1636,72 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1724,493 +1711,548 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="16.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="25.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I1" t="s">
-        <v>246</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
-        <v>247</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" s="1" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="L4" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="L5" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="L6" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" s="1" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="L13" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" s="1" t="s">
         <v>256</v>
       </c>
+      <c r="L14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2218,531 +2260,590 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:P13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I2" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="I3" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K4" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="P4" t="s">
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="I5" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="I6" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P6" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="I8" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O9" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="I10" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O10" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P10" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I11" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O11" t="s">
+      <c r="O11" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P11" t="s">
+      <c r="P11" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="I12" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O12" t="s">
+      <c r="O12" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I13" t="s">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="N13" t="s">
+      <c r="N13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O13" t="s">
+      <c r="O13" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13" s="1" t="s">
         <v>241</v>
       </c>
     </row>
@@ -2752,822 +2853,850 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="34.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="29.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="J2" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="J3" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="J4" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="J5" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="J6" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="J7" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="J15" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="J16" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="J17" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="J18" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="J19" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="J20" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="J21" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="J22" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="J23" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="J24" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="J25" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="1" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="J26" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="1" t="s">
         <v>194</v>
       </c>
+      <c r="J27" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3575,214 +3704,227 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="K3" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I4" t="s">
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I6" t="s">
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="1" t="s">
         <v>137</v>
       </c>
     </row>
@@ -3792,627 +3934,766 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:O18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="15" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I2" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I3" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I4" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K5" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K6" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="N6" t="s">
+      <c r="M6" s="1"/>
+      <c r="N6" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K7" t="s">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="N7" t="s">
+      <c r="M7" s="1"/>
+      <c r="N7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="K8" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="N8" t="s">
+      <c r="M8" s="1"/>
+      <c r="N8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="K9" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="N9" t="s">
+      <c r="M9" s="1"/>
+      <c r="N9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O9" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="K10" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="N10" t="s">
+      <c r="M10" s="1"/>
+      <c r="N10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O10" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K11" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="N11" t="s">
+      <c r="M11" s="1"/>
+      <c r="N11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O11" t="s">
+      <c r="O11" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K12" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="N12" t="s">
+      <c r="M12" s="1"/>
+      <c r="N12" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O12" t="s">
+      <c r="O12" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="K13" t="s">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="N13" t="s">
+      <c r="M13" s="1"/>
+      <c r="N13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O13" t="s">
+      <c r="O13" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K14" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="N14" t="s">
+      <c r="M14" s="1"/>
+      <c r="N14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O14" t="s">
+      <c r="O14" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="K15" t="s">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="N15" t="s">
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O15" t="s">
+      <c r="O15" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K16" t="s">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="N16" t="s">
+      <c r="M16" s="1"/>
+      <c r="N16" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O16" t="s">
+      <c r="O16" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="K17" t="s">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N17" t="s">
+      <c r="M17" s="1"/>
+      <c r="N17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O17" t="s">
+      <c r="O17" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4422,85 +4703,94 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4510,93 +4800,98 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>43</v>
       </c>
     </row>
